--- a/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
+++ b/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네트워크" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설치 목록'!$A$4:$J$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설치 목록'!$A$4:$L$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -73,7 +73,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +98,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,16 +155,34 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -522,19 +555,21 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,7 +582,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 확인. 「증빙 원문 인용」은 오른쪽 링크의 문서에 적힌 문장을 그대로 옮긴 것이다. 번호: 1 · 2 … = PC에 설치하는 프로그램(부모), 2.1 = 그 안에 들어가는 것(자식), 2.11.1 = 자식 안에 들어가는 것(손자).</t>
+          <t>2026-10-15 확인. 「구분」의 오픈소스는 OSI(Open Source Initiative)가 승인한 라이선스이며 오른쪽에 OSI 페이지를 붙였다. 오픈소스가 아닌 항목은 무료 이용 조건을 제조사 문서에서 그대로 인용했다. 「증빙 원문 인용」은 오른쪽 링크의 문서에 적힌 문장을 그대로 옮긴 것이다. 번호: 1 · 2 … = PC에 설치하는 프로그램(부모), 2.1 = 그 안에 들어가는 것(자식), 2.11.1 = 자식 안에 들어가는 것(손자).</t>
         </is>
       </c>
     </row>
@@ -589,17 +624,27 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>증빙 링크</t>
+          <t>구분</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>OSI 승인 라이선스 페이지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>증빙 링크 (라이선스 원문)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>증빙 원문 인용</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>학교 비용 · 제공</t>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>비고 (제공 · 출처의 사실)</t>
         </is>
       </c>
     </row>
@@ -639,21 +684,27 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/microsoft/WSL/blob/master/LICENSE</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/microsoft/WSL/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) Microsoft Corporation."</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -691,1929 +742,2173 @@
           <t>Docker Subscription Service Agreement</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>https://docs.docker.com/subscription/desktop-license/</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>"Docker Desktop is free for: / Small businesses (fewer than 250 employees AND less than $10 million in annual revenue) / Personal use / Education / Non-commercial open source projects"</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>없음 (출처의 'education' 항목)</t>
-        </is>
-      </c>
+      <c r="L6" s="4" t="inlineStr"/>
     </row>
     <row r="7" outlineLevel="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ emqx/emqx:5.8</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>MQTT 브로커</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/emqx/emqx</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Apache License 2.0 (기본)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/emqx/emqx/blob/v5.8.0/LICENSE</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/emqx/emqx/v5.8.0/LICENSE</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>"Source code in this repository is variously licensed under below licenses. For Default: Apache License 2.0"</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>없음 · 지원 종료 2026-02-28 (https://www.emqx.com/en/news/a-notice-on-the-emqx-5-8-open-source-version)</t>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>지원 종료 2026-02-28: https://www.emqx.com/en/news/a-notice-on-the-emqx-5-8-open-source-version</t>
         </is>
       </c>
     </row>
     <row r="8" outlineLevel="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ frangoteam/fuxa:latest</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>운전 화면(HMI)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/frangoteam/fuxa</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/frangoteam/FUXA/blob/master/LICENSE</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/frangoteam/FUXA/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2019-2025 frangoteam"</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L8" s="8" t="inlineStr"/>
     </row>
     <row r="9" outlineLevel="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ redpandadata/redpanda:v24.2.7</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>이벤트 로그</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>v24.2.7</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/redpandadata/redpanda</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Redpanda Business Source License 1.1</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/redpanda-data/redpanda/blob/dev/licenses/bsl.md</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/redpanda-data/redpanda/dev/licenses/bsl.md</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>"Redpanda Business Source License 1.1" / 공식 문서: "Users cannot provide Redpanda as a commercial streaming or queuing service to others." (https://docs.redpanda.com/streaming/24.2/get-started/licenses/)</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L9" s="8" t="inlineStr"/>
     </row>
     <row r="10" outlineLevel="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ redpandadata/console:v2.7.2</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>이벤트 로그 관리 화면 (선택 실행)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>v2.7.2</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/redpandadata/console</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Redpanda Business Source License (Community)</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>https://docs.redpanda.com/24.3/get-started/licensing/overview</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>공식 문서: Community Edition은 Redpanda BSL, 인증 · 역할 기반 권한은 Enterprise 기능</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>없음 (기본 실행 목록에 없음)</t>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>compose.yaml 주석: 선택 프로필(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="11" outlineLevel="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ timescale/timescaledb:2.17.2-pg16</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>시계열 저장소</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>2.17.2-pg16</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/timescale/timescaledb</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Apache 2.0 + Timescale License(TSL)</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/timescale/timescaledb/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>일부 오픈소스: Apache 2.0 부분은 OSI 승인, Timescale License 부분은 OSI 승인 아님</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/timescale/timescaledb/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>"Source code in this repository is variously licensed under the Apache License Version 2.0, an Apache compatible license, or the Timescale License."</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>없음 · TSL 안내: https://www.tigerdata.com/legal/licenses</t>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>TSL 안내: https://www.tigerdata.com/legal/licenses</t>
         </is>
       </c>
     </row>
     <row r="12" outlineLevel="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ grafana/grafana:11.3.0</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>분석 화면</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>11.3.0</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/grafana/grafana</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>GNU AGPL v3</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/grafana/grafana/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/agpl-v3</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/grafana/grafana/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>"GNU AFFERO GENERAL PUBLIC LICENSE Version 3, 19 November 2007"</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L12" s="8" t="inlineStr"/>
     </row>
     <row r="13" outlineLevel="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ prom/prometheus:v2.55.1</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>서비스 감시 (선택 실행)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>v2.55.1</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/r/prom/prometheus</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/prometheus/prometheus/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/prometheus/prometheus/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>없음 (기본 실행 목록에 없음)</t>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>compose.yaml 주석: 선택 프로필(기본 실행 아님)</t>
         </is>
       </c>
     </row>
     <row r="14" outlineLevel="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ neo4j:5.26-community</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>지식 그래프 DB (Neo4j Browser 포함, http://127.0.0.1:7474)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>5.26-community</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/neo4j</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>GNU GPL v3</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/neo4j/neo4j/blob/release/5.26.0/LICENSE.txt</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/gpl-3-0</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j/neo4j/release/5.26.0/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>"GNU GENERAL PUBLIC LICENSE Version 3, 29 June 2007"</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L14" s="8" t="inlineStr"/>
     </row>
     <row r="15" outlineLevel="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ nginx:1.27-alpine</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>포털 웹 화면</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>1.27-alpine</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/nginx</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>BSD 2-Clause</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-2-clause</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>https://nginx.org/LICENSE</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>"Copyright (C) 2002-2021 Igor Sysoev ... Redistribution and use in source and binary forms, with or without modification, are permitted"</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L15" s="8" t="inlineStr"/>
     </row>
     <row r="16" outlineLevel="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ python:3.12-slim</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>파이썬 서비스의 바탕 이미지 (2.11의 12개가 이 위에 빌드됨)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>자동: docker compose up 처음 실행 때 내려받음</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>3.12-slim</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>https://hub.docker.com/_/python</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Python Software Foundation License v2 (이미지 정의는 MIT)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>https://docs.python.org/3/license.html</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/license.html</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>"Python software and documentation are licensed under the Python Software Foundation License Version 2." "All Python releases are Open Source"</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L16" s="8" t="inlineStr"/>
     </row>
     <row r="17" outlineLevel="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ 자체 빌드 서비스 12개 (plant-sim · connect-ingest · cmd-gateway · connect-sink · detector · agent · process · enterprise-sim · effects-mcp · enterprise-mcp · dmn-mcp · agent-worker)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>설비 시뮬레이터 · 수집 · 명령 관문 · 저장 · 감지 · 에이전트 · 프로세스 · 업무 대역 · 도구 서버</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>자동: 교육 레포의 Dockerfile로 PC에서 빌드(바탕 2.10 + 아래 라이브러리)</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>교육 레포</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>compose.yaml · 각 서비스 Dockerfile</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>교육 레포 코드 + 아래 라이브러리 라이선스</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/uengine-oss/hyd-iot-edu/claude/hyd-handoff-work-xziutz/compose.yaml</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>유엔진 교육 레포 코드 + 아래 라이브러리</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/uengine-oss/hyd-iot-edu/claude/hyd-handoff-work-xziutz/compose.yaml</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>compose.yaml의 각 서비스 build 정의(Dockerfile: FROM python:3.12-slim, pip install -r requirements.txt)</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>교육 코드는 유엔진 제공</t>
         </is>
       </c>
     </row>
     <row r="18" outlineLevel="2">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>2.11.1</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ fastapi</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>0.115.6</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastapi/0.115.6/</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastapi/0.115.6/</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L18" s="12" t="inlineStr"/>
     </row>
     <row r="19" outlineLevel="2">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>2.11.2</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ uvicorn</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>0.34.0</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/uvicorn/0.34.0/</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-3-clause</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/uvicorn/0.34.0/</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L19" s="12" t="inlineStr"/>
     </row>
     <row r="20" outlineLevel="2">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>2.11.3</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ pydantic</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>2.10.4</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pydantic/2.10.4/</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pydantic/2.10.4/</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L20" s="12" t="inlineStr"/>
     </row>
     <row r="21" outlineLevel="2">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>2.11.4</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ paho-mqtt</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>2.1.0</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/paho-mqtt/2.1.0/</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>EPL-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/epl-2-0</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/paho-mqtt/2.1.0/</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "EPL-2.0 OR BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L21" s="12" t="inlineStr"/>
     </row>
     <row r="22" outlineLevel="2">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>2.11.5</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ aiokafka</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>0.12.0</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/aiokafka/0.12.0/</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Apache Software License</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/aiokafka/0.12.0/</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache Software License"</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L22" s="12" t="inlineStr"/>
     </row>
     <row r="23" outlineLevel="2">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>2.11.6</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ python-snappy</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>0.7.3</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/python-snappy/0.7.3/</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>BSD</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-3-clause</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/python-snappy/0.7.3/</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD"</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L23" s="12" t="inlineStr"/>
     </row>
     <row r="24" outlineLevel="2">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>2.11.7</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ lz4</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>4.3.3</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/lz4/4.3.3/</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>BSD License</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-3-clause</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/lz4/4.3.3/</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD License"</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L24" s="12" t="inlineStr"/>
     </row>
     <row r="25" outlineLevel="2">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>2.11.8</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ zstandard</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>0.23.0</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/zstandard/0.23.0/</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>BSD</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-3-clause</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/zstandard/0.23.0/</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD"</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L25" s="12" t="inlineStr"/>
     </row>
     <row r="26" outlineLevel="2">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>2.11.9</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ psycopg</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>3.2.3</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/psycopg/3.2.3/</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>GNU LGPL v3</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/lgpl-3-0</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/psycopg/3.2.3/</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="K26" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "GNU LGPL v3"</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L26" s="12" t="inlineStr"/>
     </row>
     <row r="27" outlineLevel="2">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>2.11.10</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ neo4j</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>5.27.0</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/neo4j/5.27.0/</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Apache License, Version 2.0</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/neo4j/5.27.0/</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="K27" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache License, Version 2.0"</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L27" s="12" t="inlineStr"/>
     </row>
     <row r="28" outlineLevel="2">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>2.11.11</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ anthropic</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>최신(&gt;=0.40)</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/anthropic/</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/anthropic/</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="K28" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L28" s="12" t="inlineStr"/>
     </row>
     <row r="29" outlineLevel="2">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>2.11.12</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ sqlglot</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>27.24.2</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/sqlglot/27.24.2/</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/sqlglot/27.24.2/</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="K29" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L29" s="12" t="inlineStr"/>
     </row>
     <row r="30" outlineLevel="2">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>2.11.13</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ pypdf</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>5.1.0</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pypdf/5.1.0/</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>BSD License</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/bsd-3-clause</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/pypdf/5.1.0/</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "BSD License"</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L30" s="12" t="inlineStr"/>
     </row>
     <row r="31" outlineLevel="2">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>2.11.14</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ jsonschema</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>4.26.0</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/jsonschema/4.26.0/</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/jsonschema/4.26.0/</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="K31" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "MIT"</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L31" s="12" t="inlineStr"/>
     </row>
     <row r="32" outlineLevel="2">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>2.11.15</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ cryptography</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>50.0.2</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/cryptography/50.0.2/</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Apache-2.0 OR BSD-3-Clause</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/cryptography/50.0.2/</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="K32" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache-2.0 OR BSD-3-Clause"</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L32" s="12" t="inlineStr"/>
     </row>
     <row r="33" outlineLevel="2">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>2.11.16</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ fastmcp</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>서비스 이미지 안의 파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>자동: 빌드 때 PyPI에서 pip 설치</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>2.13.0.2</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastmcp/2.13.0.2/</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>https://pypi.org/project/fastmcp/2.13.0.2/</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>PyPI 메타데이터 License: "Apache-2.0"</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L33" s="12" t="inlineStr"/>
     </row>
     <row r="34" outlineLevel="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ Supabase 로컬 이미지 (5.1 Supabase CLI가 내려받음)</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>업무 데이터베이스</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>자동: supabase start 처음 실행 때 public.ecr.aws에서 내려받음</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>CLI 2.119.0 기준</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Supabase CLI 소스 apps/cli-go/pkg/config/templates/Dockerfile · 교육 레포 it/supabase/config.toml</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/apps/cli-go/pkg/config/templates/Dockerfile</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>아래 각 이미지</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/cli/v2.119.0/apps/cli-go/pkg/config/templates/Dockerfile</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>"FROM supabase/postgres:15.19.0.002 AS pg15" "FROM library/kong:2.8.1 AS kong" "FROM postgrest/postgrest:v16.4 AS postgrest" … (교육 레포 it/supabase/config.toml에서 storage · analytics · pooler는 enabled = false)</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr"/>
     </row>
     <row r="35" outlineLevel="2">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>2.12.1</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/postgres:15.19.0.002</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>DB (PostgreSQL 15)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>15.19.0.002</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/postgres</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>The PostgreSQL License</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/postgres/blob/develop/LICENSE</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/postgresql</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/postgres/develop/LICENSE</t>
+        </is>
+      </c>
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>"The PostgreSQL License  Copyright (c) 2020, Supabase"</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L35" s="12" t="inlineStr"/>
     </row>
     <row r="36" outlineLevel="2">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>2.12.2</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ kong:2.8.1</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>API 관문</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>2.8.1</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/Kong/kong/blob/2.8.1/LICENSE</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kong/kong/2.8.1/LICENSE</t>
+        </is>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L36" s="12" t="inlineStr"/>
     </row>
     <row r="37" outlineLevel="2">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>2.12.3</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ postgrest/postgrest:v16.4</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>REST API</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>v16.4</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/postgrest/postgrest</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/PostgREST/postgrest/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/PostgREST/postgrest/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr">
         <is>
           <t>"Permission is hereby granted, free of charge, to any person"</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L37" s="12" t="inlineStr"/>
     </row>
     <row r="38" outlineLevel="2">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>2.12.4</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/gotrue:v2.197.0</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>인증</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>v2.197.0</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/gotrue</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/auth/blob/master/LICENSE</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/auth/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2021-2025 Supabase"</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L38" s="12" t="inlineStr"/>
     </row>
     <row r="39" outlineLevel="2">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>2.12.5</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/realtime:v2.140.3</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>실시간</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>v2.140.3</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/realtime</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/realtime/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/realtime/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K39" s="12" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L39" s="12" t="inlineStr"/>
     </row>
     <row r="40" outlineLevel="2">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>2.12.6</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/studio:2026.09.28-sha-5e59b60</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>DB 관리 화면</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>2026.09.28-sha-5e59b60</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/studio</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/supabase/blob/master/LICENSE</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/supabase/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L40" s="12" t="inlineStr"/>
     </row>
     <row r="41" outlineLevel="2">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>2.12.7</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/postgres-meta:v0.99.0</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>관리 화면용 메타 API</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>v0.99.0</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/postgres-meta</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/postgres-meta/blob/master/LICENSE</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/postgres-meta/master/LICENSE</t>
+        </is>
+      </c>
+      <c r="K41" s="12" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L41" s="12" t="inlineStr"/>
     </row>
     <row r="42" outlineLevel="2">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>2.12.8</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ axllent/mailpit:v1.31.3</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>메일 시험함</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>v1.31.3</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/axllent/mailpit</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/axllent/mailpit/blob/develop/LICENSE</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/axllent/mailpit/develop/LICENSE</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>"The MIT License (MIT)  Copyright (c) 2022-Now() Ralph Slooten"</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L42" s="12" t="inlineStr"/>
     </row>
     <row r="43" outlineLevel="2">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>2.12.9</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">        └ supabase/edge-runtime:v1.77.1</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>함수 실행기 (실행 여부 미확인)</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>v1.77.1</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>public.ecr.aws/supabase/edge-runtime</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>https://github.com/supabase/edge-runtime/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/supabase/edge-runtime/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) 2023 Supabase"</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2651,21 +2946,27 @@
           <t>GNU GPL v2</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/git-for-windows/git/blob/main/COPYING</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/gpl-2-0</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/git-for-windows/git/main/COPYING</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>"Note that the only valid version of the GPL as far as this project is concerned is _this_ particular version of the license (ie v2 ...)"</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2703,65 +3004,81 @@
           <t>Python Software Foundation License v2</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>https://docs.python.org/3/license.html</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/license.html</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>"Python software and documentation are licensed under the Python Software Foundation License Version 2."</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L45" s="4" t="inlineStr"/>
     </row>
     <row r="46" outlineLevel="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ 추가 라이브러리 없음</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>학생 실습 코드는 표준 라이브러리만 import (산출물/실습 코드 확인)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>학생 실습 코드의 import가 표준 라이브러리와 같은 폴더의 파일뿐</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/산출물/실습</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="I46" s="8" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/uengine-oss/hyd-iot-edu/tree/claude/hyd-handoff-work-xziutz/산출물/실습</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>실습 코드 폴더</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2799,73 +3116,85 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/nodejs/node/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/nodejs/node/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>"Node.js is licensed for use as follows: ... Permission is hereby granted, free of charge"</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L47" s="4" t="inlineStr"/>
     </row>
     <row r="48" outlineLevel="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ Supabase CLI</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>업무 데이터베이스(로컬 Supabase) 띄우기 → 2.12의 이미지를 내려받음</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>npm i -g supabase</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>2.119.0</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>https://www.npmjs.com/package/supabase/v/2.119.0</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>https://www.npmjs.com/package/supabase/v/2.119.0</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>npm 레지스트리 메타데이터 license: "MIT" (supabase@2.119.0)</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>https://registry.npmjs.org/supabase/2.119.0</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>npm 레지스트리 supabase@2.119.0: "license":"MIT"</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -2903,598 +3232,682 @@
           <t>Microsoft Software License Terms</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>https://code.visualstudio.com/license</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>"MICROSOFT SOFTWARE LICENSE TERMS ... You may use any number of copies of the software to develop and test your applications"</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
+      <c r="L49" s="4" t="inlineStr"/>
     </row>
     <row r="50" outlineLevel="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ GitHub Copilot Chat 확장</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>바이브 코딩 실습(학생의 AI 도구)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ GitHub Copilot Chat (VS Code 기본 채팅 기능)</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>바이브 코딩 실습(학생의 AI 도구). 모델은 9.1을 연결해 씀</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>따로 설치하지 않음: VS Code의 기본 채팅 에이전트로 지정되어 있음</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/microsoft/vscode/main/product.json</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>MIT (확장 소스) / GitHub License Terms for Extensions (마켓플레이스 배포판)</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>확장 소스는 오픈소스(MIT, OSI 승인) · 마켓플레이스 배포판은 GitHub 이용 조건(무료 설치)</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/microsoft/vscode-copilot-chat/main/LICENSE.txt</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>확장 소스 LICENSE.txt: "MIT License  Copyright (c) Microsoft Corporation. All rights reserved." / VS Code product.json: "defaultChatAgent": { "extensionId": "GitHub.copilot", "chatExtensionId": "GitHub.copilot-chat" … } / 배포판 이용 조건(https://github.gallery.vsassets.io/_apis/public/gallery/publisher/GitHub/extension/copilot-chat/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License): "You may install and use any number of copies of Extensions only with GitHub approved software to develop and test your applications."</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>유료 Copilot 요금제 필요 없음: VS Code 문서 "BYOK models work without signing into a GitHub account and without a Copilot plan." (9.1 링크)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ Python 확장 (ms-python.python)</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>5회차 실습 코드 실행(F5)</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>VS Code 확장 마켓플레이스에서 설치</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>최신</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>https://marketplace.visualstudio.com/items?itemName=GitHub.copilot-chat</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>확장 소스: MIT</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/microsoft/vscode-copilot-chat/blob/main/LICENSE.txt</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>https://marketplace.visualstudio.com/items?itemName=ms-python.python</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>"Copyright (c) Microsoft Corporation. All rights reserved. MIT License" / "The Python extension automatically installs other extensions as optional dependencies"</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52" outlineLevel="2">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>6.2.1</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        └ Pylance (Python 확장이 함께 설치)</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>파이썬 언어 기능</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>자동: 6.2 설치 때 함께(지울 수 있음)</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>https://marketplace.visualstudio.com/items?itemName=ms-python.vscode-pylance</t>
+        </is>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Microsoft Software License Terms (Microsoft Pylance Extension for Visual Studio Code)</t>
+        </is>
+      </c>
+      <c r="H52" s="11" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/vscode-pylance/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>"You may install and use any number of copies of the software only with Microsoft Visual Studio, Visual Studio for Mac, Visual Studio Code ... to develop and test your applications." / Python 확장 라이선스: "The Pylance extension is only available in binary form and is released under a Microsoft proprietary license"</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53" outlineLevel="2">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>6.2.2</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        └ Python Debugger (Python 확장이 함께 설치)</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>디버거</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>자동: 6.2 설치 때 함께(지울 수 있음)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>최신</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>https://marketplace.visualstudio.com/items?itemName=ms-python.debugpy</t>
+        </is>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/mit</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
         <is>
           <t>"MIT License  Copyright (c) Microsoft Corporation."</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>없음 · Copilot 이용 계정 · 라이선스는 유엔진 제공 (9.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ Python 확장 (ms-python.python)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>5회차 실습 코드 실행(F5)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>VS Code 확장 마켓플레이스에서 설치</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>최신</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>https://marketplace.visualstudio.com/items?itemName=ms-python.python</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/microsoft/vscode-python/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>"Copyright (c) Microsoft Corporation. All rights reserved.  MIT License"</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="2">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>6.2.1</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        └ Pylance (Python 확장이 함께 설치)</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>파이썬 언어 기능</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>자동: 6.2 설치 때 함께</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>최신</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>https://marketplace.visualstudio.com/items?itemName=ms-python.vscode-pylance</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>미확인 (원문 페이지를 이 환경에서 읽지 못함)</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>https://marketplace.visualstudio.com/items/ms-python.vscode-pylance/license</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Notion 데스크톱 앱</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>1회차 실습: 학습노트</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>설치 파일</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>최신 (Windows x64 / ARM64)</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.notion.com/ko/desktop</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Notion 이용 약관 (Free 플랜)</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.notion.com/pricing</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>Free 플랜: "$0" per member / month — "For individuals to organize personal projects and life."</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>없음 (Free 플랜)</t>
-        </is>
-      </c>
+      <c r="L53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Notion 데스크톱 앱</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1회차 실습: 학습노트</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>설치 파일</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>최신 (Windows x64 / ARM64)</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.notion.com/ko/desktop</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Notion 이용 약관 (Free 플랜)</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.notion.com/pricing</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Free 플랜: "$0" per member / month — "For individuals to organize personal projects and life."</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>웹 서비스 (설치 없음)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>브라우저</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
-      <c r="G54" s="4" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
-    </row>
-    <row r="55" outlineLevel="1">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">    └ arrows.app</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>1회차 실습: 관계 그리기</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>설치 없음(웹)</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>https://arrows.app/</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/neo4j-labs/arrows.app/blob/main/LICENSE</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>오픈소스 (OSI 승인 라이선스)</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>https://opensource.org/license/apache-2-0</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/neo4j-labs/arrows.app/main/LICENSE</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>"Apache License Version 2.0, January 2004"</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="L56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ GitHub 계정</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Copilot 로그인</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>웹 가입</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ GitHub 계정 (Copilot Free)</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Copilot 인라인 제안(코드 자동완성)을 쓸 때 로그인. 채팅은 9.1로 계정 없이 됨</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>웹 가입 (무료)</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>https://github.com/</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>GitHub 이용 약관</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>https://docs.github.com/site-policy/github-terms/github-terms-of-service</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>없음 (Copilot 이용권은 9.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>GitHub 이용 약관 · Copilot Free 플랜</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>오픈소스 아님 · 무료 이용 조건은 인용 참고</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/docs/setup/copilot</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>"Without a plan, signing in enrolls an eligible account in Copilot Free." "If you don't have a Copilot subscription yet, you'll be signed up for the Copilot Free plan and get a monthly allowance of inline suggestions and AI credits."</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>계정 없이 안 되는 기능 (https://code.visualstudio.com/docs/agent-customization/language-models): "Some features still require a GitHub account: semantic search, inline suggestions (code completions), and features that rely on embeddings."</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>유엔진 제공 (학교 설치 · 비용 없음)</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>유엔진 제공 (학교 설치 대상 아님)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>유엔진 제공 · 지불</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ GitHub Copilot 이용 계정 · 라이선스</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>6.1 확장에서 쓰는 AI 서비스</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>유엔진이 제공</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    └ AI 모델 (LiteLLM 중계) — 수업에서 쓰는 모든 AI</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>① Copilot 채팅의 커스텀 모델(6.1에 연결) ② 시스템 에이전트의 요약 · 문서 지식 추출</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>유엔진이 주소 · 키를 알려 줌 (VS Code: 채팅 모델 고르기 → 언어 모델 관리 → Custom Endpoint)</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/features/copilot/plans</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>GitHub Copilot 이용 약관</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>https://github.com/features/copilot/plans</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>없음 (유엔진 제공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ LLM API 키 · 서버</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>에이전트 요약 · 문서 지식 추출</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>유엔진이 제공</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>없음 (유엔진 제공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    └ Claude Code CLI (강사 PC 호스트 워커)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>시연 때 에이전트 작업 처리</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>강사 PC에만 설치</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>2.1.292</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>없음 (강사 PC, 학교 설치 대상 아님)</t>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/docs/agent-customization/language-models</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>유엔진 제공 (학교 설치 · 결제 없음)</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>유엔진 제공 · 지불</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>https://code.visualstudio.com/docs/agent-customization/language-models</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>"Bring Your Own Key (BYOK) lets you connect to any compatible model provider while still using the VS Code chat experience and tools." "BYOK models work without signing into a GitHub account and without a Copilot plan." "The Custom Endpoint provider lets you connect any compatible API endpoint to chat in VS Code." / 과금 (https://code.visualstudio.com/docs/setup/copilot): "If you use a Claude bring-your-own-key (BYOK) configuration, a ChatGPT subscription, or your own model credentials, that provider manages usage and billing instead."</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>이용 비용은 유엔진 지불</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J60"/>
+  <autoFilter ref="A4:L59"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3523,177 +3936,177 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>무엇을 받는가</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>관련 번호</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>registry-1.docker.io, auth.docker.io, production.cloudflare.docker.com</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>도커 이미지(Docker Hub)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>2.1~2.10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>public.ecr.aws</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Supabase 이미지</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>pypi.org, files.pythonhosted.org</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>2.11.x</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>registry.npmjs.org</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Supabase CLI</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>marketplace.visualstudio.com</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>VS Code 확장</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>6.1 · 6.2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>github.com</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>GitHub 로그인 · Copilot</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>8.2 · 9.1</t>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>github.com, api.github.com</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>GitHub 로그인 · Copilot 인라인 제안</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>8.2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>www.notion.so, www.notion.com</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>arrows.app</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>관계 그리기</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>유엔진이 알려 주는 LLM 서버 주소</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>LLM</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>9.2</t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>유엔진이 알려 주는 AI 모델 주소 (LiteLLM)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>AI 모델 (Copilot 채팅 · 시스템 에이전트)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>9.1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>대표 주소다. 제조사가 공개한 전체 방화벽 목록은 각 제조사 문서를 따른다.</t>
         </is>

--- a/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
+++ b/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설치 목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네트워크" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설치 명령어" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네트워크" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'설치 목록'!$A$4:$L$59</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,12 +69,27 @@
       <u val="single"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +131,11 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -142,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,11 +206,31 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -778,7 +819,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -840,7 +881,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -898,7 +939,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -952,7 +993,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1010,7 +1051,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1072,7 +1113,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1130,7 +1171,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1192,7 +1233,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1250,7 +1291,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1303,12 +1344,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>파이썬 서비스의 바탕 이미지 (2.11의 12개가 이 위에 빌드됨)</t>
+          <t>파이썬 서비스의 바탕 이미지 (2.11의 11개가 이 위에 빌드됨)</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>자동: docker compose up 처음 실행 때 내려받음</t>
+          <t>docker pull (「설치 명령어」 시트 2단계)</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1356,7 +1397,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    └ 자체 빌드 서비스 12개 (plant-sim · connect-ingest · cmd-gateway · connect-sink · detector · agent · process · enterprise-sim · effects-mcp · enterprise-mcp · dmn-mcp · agent-worker)</t>
+          <t xml:space="preserve">    └ 자체 빌드 서비스 11개 (plant-sim · connect-ingest · cmd-gateway · connect-sink · detector · agent · process · enterprise-sim · effects-mcp · enterprise-mcp · dmn-mcp)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1366,7 +1407,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>자동: 교육 레포의 Dockerfile로 PC에서 빌드(바탕 2.10 + 아래 라이브러리)</t>
+          <t>공개 저장소에 없음: 유엔진이 이미지 파일(tar)로 전달 → docker load, 또는 교육 레포에서 docker compose build (「설치 명령어」 시트 4단계)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1402,7 +1443,7 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>교육 코드는 유엔진 제공</t>
+          <t>교육 코드는 유엔진 제공. compose.yaml의 agent-worker(Claude Code 포함)는 수업에서 실행하지 않으므로 목록에서 뺌</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2393,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>자동: supabase start 처음 실행 때 public.ecr.aws에서 내려받음</t>
+          <t>자동: supabase start 처음 실행 때 public.ecr.aws/supabase/&lt;이름&gt;으로 내려받음 (미리 받기: 「설치 명령어」 시트 3단계)</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -2474,7 +2515,7 @@
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>public.ecr.aws/supabase</t>
+          <t>public.ecr.aws/supabase/kong</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -2532,7 +2573,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>public.ecr.aws/postgrest/postgrest</t>
+          <t>public.ecr.aws/supabase/postgrest</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -2822,7 +2863,7 @@
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>public.ecr.aws/axllent/mailpit</t>
+          <t>public.ecr.aws/supabase/mailpit</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -3330,7 +3371,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>VS Code 확장 마켓플레이스에서 설치</t>
+          <t>code --install-extension ms-python.python (「설치 명령어」 시트 1단계)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -3920,6 +3961,632 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>설치 명령어 — 명령으로 설치 · 내려받는 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>프로그램(WSL 제외)은 「설치 목록」 시트의 「받는 곳」에서 공식 설치 파일로 설치한다. 아래는 명령으로 하는 것만 적었다. 명령은 PowerShell · 명령 프롬프트 · bash 어디서나 같다. 단계마다 마지막 줄은 그 단계의 명령 전체를 한 칸에 모은 것이다(한 번에 복사).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>명령어</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>설치 목록 번호</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>1. PC 준비 (관리자 PowerShell, 끝나면 다시 시작)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr"/>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>wsl --install</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Docker Desktop의 기반</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr"/>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>npm install -g supabase@2.119.0</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Node.js(5) 설치 뒤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>code --install-extension ms-python.python</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>VS Code(6) 설치 뒤. Pylance(6.2.1) · Python Debugger(6.2.2)가 함께 설치됨. Copilot 채팅(6.1)은 VS Code 기본 포함이라 명령 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="49" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>한 번에 복사</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>wsl --install
+npm install -g supabase@2.119.0
+code --install-extension ms-python.python</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>2. 도커 이미지 내려받기 — Docker Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>docker pull emqx/emqx:5.8</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr"/>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>docker pull frangoteam/fuxa:latest</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>태그가 latest라 받는 날의 최신판</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr"/>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>docker pull redpandadata/redpanda:v24.2.7</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr"/>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>docker pull timescale/timescaledb:2.17.2-pg16</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr"/>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>docker pull grafana/grafana:11.3.0</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr"/>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>docker pull neo4j:5.26-community</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr"/>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>docker pull nginx:1.27-alpine</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr"/>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>docker pull python:3.12-slim</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>2.11을 직접 빌드할 때도 바탕</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr"/>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>docker pull redpandadata/console:v2.7.2</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>선택 실행(기본 실행 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr"/>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>docker pull prom/prometheus:v2.55.1</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>선택 실행(기본 실행 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="154" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>한 번에 복사</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>docker pull emqx/emqx:5.8
+docker pull frangoteam/fuxa:latest
+docker pull redpandadata/redpanda:v24.2.7
+docker pull timescale/timescaledb:2.17.2-pg16
+docker pull grafana/grafana:11.3.0
+docker pull neo4j:5.26-community
+docker pull nginx:1.27-alpine
+docker pull python:3.12-slim
+docker pull redpandadata/console:v2.7.2
+docker pull prom/prometheus:v2.55.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>3. 도커 이미지 내려받기 — Supabase (supabase start가 찾는 이름 그대로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr"/>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>2.12.1</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr"/>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/kong:2.8.1</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>2.12.2</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr"/>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/postgrest:v16.4</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>2.12.3</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr"/>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/gotrue:v2.197.0</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>2.12.4</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr"/>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/realtime:v2.140.3</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>2.12.5</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/studio:2026.09.28-sha-5e59b60</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>2.12.6</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr"/>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/postgres-meta:v0.99.0</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>2.12.7</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr"/>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/mailpit:v1.31.3</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>2.12.8</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr"/>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/edge-runtime:v1.77.1</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>2.12.9</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr"/>
+    </row>
+    <row r="34" ht="139" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>한 번에 복사</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002
+docker pull public.ecr.aws/supabase/kong:2.8.1
+docker pull public.ecr.aws/supabase/postgrest:v16.4
+docker pull public.ecr.aws/supabase/gotrue:v2.197.0
+docker pull public.ecr.aws/supabase/realtime:v2.140.3
+docker pull public.ecr.aws/supabase/studio:2026.09.28-sha-5e59b60
+docker pull public.ecr.aws/supabase/postgres-meta:v0.99.0
+docker pull public.ecr.aws/supabase/mailpit:v1.31.3
+docker pull public.ecr.aws/supabase/edge-runtime:v1.77.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>4. 자체 빌드 이미지 11개 넣기 — 방법 A: 유엔진이 전달한 이미지 파일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr"/>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>docker load -i hyd-iot-edu-images.tar</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>파일은 유엔진이 따로 전달(엑셀에 담을 수 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>4. 자체 빌드 이미지 11개 넣기 — 방법 B: 교육 레포에서 직접 빌드 (pypi.org 접속 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr"/>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr"/>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>cd hyd-iot-edu</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr"/>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>docker compose --profile ot --profile backbone --profile detect --profile knowledge --profile agent --profile enterprise --profile process --profile cliagents build plant-sim connect-ingest cmd-gateway connect-sink detector agent process enterprise-sim effects-mcp enterprise-mcp dmn-mcp</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>프로필 8개를 모두 켜야 서비스 사이 의존이 풀린다(일부만 켜면 "depends on undefined service" 오류)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="49" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>한 번에 복사</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git
+cd hyd-iot-edu
+docker compose --profile ot --profile backbone --profile detect --profile knowledge --profile agent --profile enterprise --profile process --profile cliagents build plant-sim connect-ingest cmd-gateway connect-sink detector agent process enterprise-sim effects-mcp enterprise-mcp dmn-mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>5. 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr"/>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>docker images</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>2 · 3단계 19개(선택 2개 포함)와 4단계 hyd-iot-edu-* 11개가 보이면 된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>확인한 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>2단계 이미지 이름 · 태그: 교육 레포 compose.yaml의 image 값 그대로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>3단계 이미지 이름: Supabase CLI v2.119.0 소스의 규칙 return registry + '/supabase/' + imageName (apps/cli-go/internal/utils/docker.go, 기본 레지스트리 "public.ecr.aws")과 태그 목록(apps/cli-go/pkg/config/templates/Dockerfile). 레지스트리 조회는 postgres-meta만 응답 200을 확인했고 나머지 8개는 요청 제한(429)으로 확인하지 못했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>4단계 이미지 이름: compose.yaml의 name: hyd-iot-edu에 따라 hyd-iot-edu-&lt;서비스&gt;로 만들어진다. 방법 B 명령은 docker compose config로 검사했다(프로필 8개: 통과, 일부 프로필: depends on undefined service 오류). 빌드 자체는 이 문서를 만든 환경에서 돌리지 않았다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A36:D36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3936,177 +4603,177 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>주소</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>무엇을 받는가</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>관련 번호</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>registry-1.docker.io, auth.docker.io, production.cloudflare.docker.com</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>도커 이미지(Docker Hub)</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>2.1~2.10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>public.ecr.aws</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Supabase 이미지</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>pypi.org, files.pythonhosted.org</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>파이썬 라이브러리</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>2.11.x</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>registry.npmjs.org</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Supabase CLI</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>marketplace.visualstudio.com</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>VS Code 확장</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>6.1 · 6.2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>github.com, api.github.com</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>GitHub 로그인 · Copilot 인라인 제안</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>www.notion.so, www.notion.com</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>arrows.app</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>관계 그리기</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>유엔진이 알려 주는 AI 모델 주소 (LiteLLM)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>AI 모델 (Copilot 채팅 · 시스템 에이전트)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>대표 주소다. 제조사가 공개한 전체 방화벽 목록은 각 제조사 문서를 따른다.</t>
         </is>

--- a/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
+++ b/산출물/설치/HYD_교육_설치목록_라이선스.xlsx
@@ -765,17 +765,17 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>설치 파일</t>
+          <t>설치 파일 (Windows x64)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>엔진 29.7.2 (제작자 PC 2026-10-03)</t>
+          <t>4.86.0 (Docker Engine v29.7.2 — 제작자 PC 엔진 버전)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>https://www.docker.com/products/docker-desktop/</t>
+          <t>https://desktop.docker.com/win/main/amd64/236216/Docker%20Desktop%20Installer.exe</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -799,7 +799,11 @@
           <t>"Docker Desktop is free for: / Small businesses (fewer than 250 employees AND less than $10 million in annual revenue) / Personal use / Education / Non-commercial open source projects"</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>버전 근거: 공식 릴리스 노트 https://docs.docker.com/desktop/release-notes/ 「4.86.0 2026-08-10 … Updates Docker Engine v29.7.2」</t>
+        </is>
+      </c>
     </row>
     <row r="7" outlineLevel="1">
       <c r="A7" s="8" t="inlineStr">
@@ -2969,17 +2973,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>설치 파일</t>
+          <t>설치 파일 (Windows x64)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>2.56.0.2 (2026-10-15 공식 최신)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>https://git-scm.com/download/win</t>
+          <t>https://github.com/git-for-windows/git/releases/download/v2.56.0.windows.2/Git-2.56.0.2-64-bit.exe</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2999,15 +3003,19 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/git-for-windows/git/main/COPYING</t>
+          <t>https://raw.githubusercontent.com/git-for-windows/git/v2.56.0.windows.2/COPYING</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>"Note that the only valid version of the GPL as far as this project is concerned is _this_ particular version of the license (ie v2 ...)"</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr"/>
+          <t>"Note that the only valid version of the GPL as far as this project is concerned is _this_ particular version of the license (ie v2, not v2.2 or v3.x or whatever), unless explicitly otherwise stated."</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>버전 근거: https://gitforwindows.org/latest-version.txt → 2.56.0.2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3027,17 +3035,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>설치 파일 (python.org 공식판)</t>
+          <t>설치 파일 (python.org 공식판, Windows x64)</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>3.14.7</t>
+          <t>3.14.7 (제작자 PC 검증 버전)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>https://www.python.org/downloads/</t>
+          <t>https://www.python.org/ftp/python/3.14.7/python-3.14.7-amd64.exe</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3057,15 +3065,19 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>https://docs.python.org/3/license.html</t>
+          <t>https://raw.githubusercontent.com/python/cpython/v3.14.7/LICENSE</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>"Python software and documentation are licensed under the Python Software Foundation License Version 2."</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr"/>
+          <t>v3.14.7 LICENSE: "All Python releases are Open Source (see https://opensource.org for the Open Source Definition)." "PYTHON SOFTWARE FOUNDATION LICENSE VERSION 2"</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>공식 문서 https://docs.python.org/3.14/license.html: "Python software and documentation are licensed under the Python Software Foundation License Version 2."</t>
+        </is>
+      </c>
     </row>
     <row r="46" outlineLevel="1">
       <c r="A46" s="8" t="inlineStr">
@@ -3139,17 +3151,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>설치 파일</t>
+          <t>설치 파일 (Windows x64 .msi)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>24.22.0 (24 LTS의 2026-10-15 최신)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>https://nodejs.org/</t>
+          <t>https://nodejs.org/dist/v24.22.0/node-v24.22.0-x64.msi</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -3169,15 +3181,19 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/nodejs/node/main/LICENSE</t>
+          <t>https://raw.githubusercontent.com/nodejs/node/v24.22.0/LICENSE</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>"Node.js is licensed for use as follows: ... Permission is hereby granted, free of charge"</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr"/>
+          <t>v24.22.0 LICENSE: "Node.js is licensed for use as follows: … Permission is hereby granted, free of charge, to any person obtaining a copy of this software"</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>버전 근거: https://nodejs.org/dist/index.json (v24.22.0, 2026-10-14, LTS Krypton). 제작자 PC 기록은 주 버전 24</t>
+        </is>
+      </c>
     </row>
     <row r="48" outlineLevel="1">
       <c r="A48" s="8" t="inlineStr">
@@ -3255,22 +3271,22 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>설치 파일</t>
+          <t>설치 파일 (Windows x64, 사용자 설치판 · 학교 일괄은 시스템 설치판 https://update.code.visualstudio.com/1.142.0/win32-x64/stable)</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>1.142.0 (2026-10-15 공식 최신)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>https://code.visualstudio.com/</t>
+          <t>https://update.code.visualstudio.com/1.142.0/win32-x64-user/stable</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Microsoft Software License Terms</t>
+          <t>Microsoft Software License Terms (배포판) · 소스는 MIT</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -3286,10 +3302,14 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>"MICROSOFT SOFTWARE LICENSE TERMS ... You may use any number of copies of the software to develop and test your applications"</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr"/>
+          <t>"You may use any number of copies of the software to develop and test your applications, including deployment within your internal corporate network." / FAQ https://code.visualstudio.com/docs/supporting/faq: "Is VS Code free? Yes, VS Code is free for private or commercial use."</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>소스 1.142.0 LICENSE.txt: "MIT License  Copyright (c) 2015 - present Microsoft Corporation" (https://raw.githubusercontent.com/microsoft/vscode/1.142.0/LICENSE.txt). 버전 근거: https://update.code.visualstudio.com/api/releases/stable</t>
+        </is>
+      </c>
     </row>
     <row r="50" outlineLevel="1">
       <c r="A50" s="8" t="inlineStr">
@@ -3314,7 +3334,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>VS Code 1.142.0이 맞는 판을 설정</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -3371,12 +3391,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>code --install-extension ms-python.python (「설치 명령어」 시트 1단계)</t>
+          <t>code --install-extension ms-python.python@2026.10.0 (「설치 명령어」 시트 1단계)</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>2026.10.0 (2026-10-15 최신 안정판)</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
@@ -3401,7 +3421,7 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/python/2026.10.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -3429,12 +3449,12 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>자동: 6.2 설치 때 함께(지울 수 있음)</t>
+          <t>code --install-extension ms-python.vscode-pylance@2026.4.1 (지울 수 있음)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>2026.4.1</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -3455,7 +3475,7 @@
       <c r="I52" s="12" t="inlineStr"/>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/vscode-pylance/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/vscode-pylance/2026.4.1/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -3483,12 +3503,12 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>자동: 6.2 설치 때 함께(지울 수 있음)</t>
+          <t>code --install-extension ms-python.debugpy@2026.6.0 (지울 수 있음)</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>최신</t>
+          <t>2026.6.0</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -3513,7 +3533,7 @@
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/latest/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
+          <t>https://ms-python.gallery.vsassets.io/_apis/public/gallery/publisher/ms-python/extension/debugpy/2026.6.0/assetbyname/Microsoft.VisualStudio.Services.Content.License</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -3541,17 +3561,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>설치 파일</t>
+          <t>설치 파일 (Windows x64)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>최신 (Windows x64 / ARM64)</t>
+          <t>7.38.1 (2026-10-15 공식 최신)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>https://www.notion.com/ko/desktop</t>
+          <t>https://desktop-release.notion-static.com/Notion%20Setup%207.38.1.exe</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3575,7 +3595,11 @@
           <t>Free 플랜: "$0" per member / month — "For individuals to organize personal projects and life."</t>
         </is>
       </c>
-      <c r="L54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>버전 근거: 공식 다운로드 https://www.notion.so/desktop/windows/download 가 Notion Setup 7.38.1.exe로 이어짐</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3961,7 +3985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4053,70 +4077,72 @@
       <c r="A8" s="19" t="inlineStr"/>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>code --install-extension ms-python.python</t>
+          <t>code --install-extension ms-python.vscode-pylance@2026.4.1</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
+          <t>6.2.1</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>VS Code(6) 설치 뒤. 버전을 고정하려고 Python 확장보다 먼저 설치</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>code --install-extension ms-python.debugpy@2026.6.0</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>6.2.2</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>code --install-extension ms-python.python@2026.10.0</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>VS Code(6) 설치 뒤. Pylance(6.2.1) · Python Debugger(6.2.2)가 함께 설치됨. Copilot 채팅(6.1)은 VS Code 기본 포함이라 명령 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="49" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Copilot 채팅(6.1)은 VS Code 기본 포함이라 명령 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="79" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>wsl --install
 npm install -g supabase@2.119.0
-code --install-extension ms-python.python</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+code --install-extension ms-python.vscode-pylance@2026.4.1
+code --install-extension ms-python.debugpy@2026.6.0
+code --install-extension ms-python.python@2026.10.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>2. 도커 이미지 내려받기 — Docker Hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr"/>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>docker pull emqx/emqx:5.8</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr"/>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>docker pull frangoteam/fuxa:latest</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>태그가 latest라 받는 날의 최신판</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4150,12 @@
       <c r="A14" s="19" t="inlineStr"/>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>docker pull redpandadata/redpanda:v24.2.7</t>
+          <t>docker pull emqx/emqx:5.8</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr"/>
@@ -4138,26 +4164,30 @@
       <c r="A15" s="19" t="inlineStr"/>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>docker pull timescale/timescaledb:2.17.2-pg16</t>
+          <t>docker pull frangoteam/fuxa:latest</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr"/>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>태그가 latest라 받는 날의 최신판</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>docker pull grafana/grafana:11.3.0</t>
+          <t>docker pull redpandadata/redpanda:v24.2.7</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr"/>
@@ -4166,12 +4196,12 @@
       <c r="A17" s="19" t="inlineStr"/>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>docker pull neo4j:5.26-community</t>
+          <t>docker pull timescale/timescaledb:2.17.2-pg16</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr"/>
@@ -4180,12 +4210,12 @@
       <c r="A18" s="19" t="inlineStr"/>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>docker pull nginx:1.27-alpine</t>
+          <t>docker pull grafana/grafana:11.3.0</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr"/>
@@ -4194,63 +4224,91 @@
       <c r="A19" s="19" t="inlineStr"/>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>docker pull python:3.12-slim</t>
+          <t>docker pull neo4j:5.26-community</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>2.11을 직접 빌드할 때도 바탕</t>
-        </is>
-      </c>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>docker pull redpandadata/console:v2.7.2</t>
+          <t>docker pull nginx:1.27-alpine</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>선택 실행(기본 실행 아님)</t>
-        </is>
-      </c>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr"/>
       <c r="B21" s="20" t="inlineStr">
         <is>
+          <t>docker pull python:3.12-slim</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>2.11을 직접 빌드할 때도 바탕</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr"/>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>docker pull redpandadata/console:v2.7.2</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>선택 실행(기본 실행 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr"/>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
           <t>docker pull prom/prometheus:v2.55.1</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>선택 실행(기본 실행 아님)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="154" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+    <row r="24" ht="154" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>docker pull emqx/emqx:5.8
 docker pull frangoteam/fuxa:latest
@@ -4265,51 +4323,23 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>3. 도커 이미지 내려받기 — Supabase (supabase start가 찾는 이름 그대로)</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr"/>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>2.12.1</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr"/>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>docker pull public.ecr.aws/supabase/kong:2.8.1</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>2.12.2</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr"/>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/postgrest:v16.4</t>
+          <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002</t>
         </is>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>2.12.3</t>
+          <t>2.12.1</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr"/>
@@ -4318,12 +4348,12 @@
       <c r="A28" s="19" t="inlineStr"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/gotrue:v2.197.0</t>
+          <t>docker pull public.ecr.aws/supabase/kong:2.8.1</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>2.12.4</t>
+          <t>2.12.2</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr"/>
@@ -4332,12 +4362,12 @@
       <c r="A29" s="19" t="inlineStr"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/realtime:v2.140.3</t>
+          <t>docker pull public.ecr.aws/supabase/postgrest:v16.4</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>2.12.5</t>
+          <t>2.12.3</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr"/>
@@ -4346,12 +4376,12 @@
       <c r="A30" s="19" t="inlineStr"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/studio:2026.09.28-sha-5e59b60</t>
+          <t>docker pull public.ecr.aws/supabase/gotrue:v2.197.0</t>
         </is>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>2.12.6</t>
+          <t>2.12.4</t>
         </is>
       </c>
       <c r="D30" s="19" t="inlineStr"/>
@@ -4360,12 +4390,12 @@
       <c r="A31" s="19" t="inlineStr"/>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/postgres-meta:v0.99.0</t>
+          <t>docker pull public.ecr.aws/supabase/realtime:v2.140.3</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>2.12.7</t>
+          <t>2.12.5</t>
         </is>
       </c>
       <c r="D31" s="19" t="inlineStr"/>
@@ -4374,12 +4404,12 @@
       <c r="A32" s="19" t="inlineStr"/>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>docker pull public.ecr.aws/supabase/mailpit:v1.31.3</t>
+          <t>docker pull public.ecr.aws/supabase/studio:2026.09.28-sha-5e59b60</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>2.12.8</t>
+          <t>2.12.6</t>
         </is>
       </c>
       <c r="D32" s="19" t="inlineStr"/>
@@ -4388,23 +4418,51 @@
       <c r="A33" s="19" t="inlineStr"/>
       <c r="B33" s="20" t="inlineStr">
         <is>
+          <t>docker pull public.ecr.aws/supabase/postgres-meta:v0.99.0</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>2.12.7</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr"/>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>docker pull public.ecr.aws/supabase/mailpit:v1.31.3</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>2.12.8</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr"/>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
           <t>docker pull public.ecr.aws/supabase/edge-runtime:v1.77.1</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>2.12.9</t>
         </is>
       </c>
-      <c r="D33" s="19" t="inlineStr"/>
-    </row>
-    <row r="34" ht="139" customHeight="1">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr"/>
+    </row>
+    <row r="36" ht="139" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>docker pull public.ecr.aws/supabase/postgres:15.19.0.002
 docker pull public.ecr.aws/supabase/kong:2.8.1
@@ -4418,91 +4476,91 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>4. 자체 빌드 이미지 11개 넣기 — 방법 A: 유엔진이 전달한 이미지 파일</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr"/>
-      <c r="B37" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>docker load -i hyd-iot-edu-images.tar</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>파일은 유엔진이 따로 전달(엑셀에 담을 수 없음)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>4. 자체 빌드 이미지 11개 넣기 — 방법 B: 교육 레포에서 직접 빌드 (pypi.org 접속 필요)</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr"/>
-      <c r="B40" s="20" t="inlineStr">
-        <is>
-          <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git</t>
-        </is>
-      </c>
-      <c r="C40" s="19" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr"/>
-      <c r="B41" s="20" t="inlineStr">
-        <is>
-          <t>cd hyd-iot-edu</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr"/>
       <c r="B42" s="20" t="inlineStr">
         <is>
+          <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr"/>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>cd hyd-iot-edu</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr"/>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
           <t>docker compose --profile ot --profile backbone --profile detect --profile knowledge --profile agent --profile enterprise --profile process --profile cliagents build plant-sim connect-ingest cmd-gateway connect-sink detector agent process enterprise-sim effects-mcp enterprise-mcp dmn-mcp</t>
         </is>
       </c>
-      <c r="C42" s="19" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>2.11</t>
         </is>
       </c>
-      <c r="D42" s="19" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>프로필 8개를 모두 켜야 서비스 사이 의존이 풀린다(일부만 켜면 "depends on undefined service" 오류)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49" customHeight="1">
-      <c r="A43" s="21" t="inlineStr">
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>한 번에 복사</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>git clone https://github.com/uengine-oss/hyd-iot-edu.git
 cd hyd-iot-edu
@@ -4510,54 +4568,54 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>5. 확인</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr"/>
-      <c r="B46" s="20" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr"/>
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>docker images</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>2 · 3단계 19개(선택 2개 포함)와 4단계 hyd-iot-edu-* 11개가 보이면 된다</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>확인한 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>2단계 이미지 이름 · 태그: 교육 레포 compose.yaml의 image 값 그대로.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>3단계 이미지 이름: Supabase CLI v2.119.0 소스의 규칙 return registry + '/supabase/' + imageName (apps/cli-go/internal/utils/docker.go, 기본 레지스트리 "public.ecr.aws")과 태그 목록(apps/cli-go/pkg/config/templates/Dockerfile). 레지스트리 조회는 postgres-meta만 응답 200을 확인했고 나머지 8개는 요청 제한(429)으로 확인하지 못했다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>2단계 이미지 이름 · 태그: 교육 레포 compose.yaml의 image 값 그대로.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>3단계 이미지 이름: Supabase CLI v2.119.0 소스의 규칙 return registry + '/supabase/' + imageName (apps/cli-go/internal/utils/docker.go, 기본 레지스트리 "public.ecr.aws")과 태그 목록(apps/cli-go/pkg/config/templates/Dockerfile). 레지스트리 조회는 postgres-meta만 응답 200을 확인했고 나머지 8개는 요청 제한(429)으로 확인하지 못했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>4단계 이미지 이름: compose.yaml의 name: hyd-iot-edu에 따라 hyd-iot-edu-&lt;서비스&gt;로 만들어진다. 방법 B 명령은 docker compose config로 검사했다(프로필 8개: 통과, 일부 프로필: depends on undefined service 오류). 빌드 자체는 이 문서를 만든 환경에서 돌리지 않았다.</t>
         </is>
@@ -4566,15 +4624,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A49:D49"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
